--- a/data/sources/countries/dominican_republic.xlsx
+++ b/data/sources/countries/dominican_republic.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,7 +728,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -839,7 +743,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Government of China</t>
+          <t>Gobierno de la Republica Popular China</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -896,20 +800,20 @@
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://presidencia.gob.do/noticias/republica-dominicana-y-la-republica-popular-china-firman-instrumentos-de-cooperacion</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/america/agencias/2025/09/08/republica-dominicana-y-china-suscriben-un-convenio-de-cooperacion-economica-para-proyectos-de-desarrollo/</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://presidencia.gob.do/noticias/republica-dominicana-y-la-republica-popular-china-firman-instrumentos-de-cooperacion</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>https://www.infobae.com/america/agencias/2025/09/08/republica-dominicana-y-china-suscriben-un-convenio-de-cooperacion-economica-para-proyectos-de-desarrollo/</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://revistamercado.do/money-invest/rd-y-china-acuerdan-cooperacion-por-us40-millones/</t>
         </is>
@@ -939,7 +843,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -954,7 +858,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Huawei Technologies Dominicana, S.R.L.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1011,20 +915,20 @@
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://www.diariolibre.com/economia/huawei-busca-que-repblica-dominicana-sea-centro-regional-CODL351399</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>https://hoy.com.do/economia/huawei-dominicana-cierra-2022-con-positivo-balance_941954.html</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://www.diariolibre.com/economia/huawei-busca-que-repblica-dominicana-sea-centro-regional-CODL351399</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>https://hoy.com.do/economia/huawei-dominicana-cierra-2022-con-positivo-balance_941954.html</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://ayuntamientosancristobal.gob.do/el-instituto-dominicano-de-las-telecomunicaciones-indotel-y-huawei-technologies-dominicana-s-r-l-firman-un-acuerdo-para-la-cooperacion-tecnologica/</t>
         </is>
@@ -1054,7 +958,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -1069,7 +973,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Unidentified</t>
+          <t>Varias empresas chinas</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1126,25 +1030,20 @@
       <c r="BA4" t="n">
         <v>3</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>1</v>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://listindiario.com/la-republica/gobierno/20251129/china-republica-dominicana-alianza-mueve-comercio-inversion-tecnologia_884203.html</t>
+        </is>
+      </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.ccrde.org/61-china-ve-enormes-oportunidades-de-comercio-e-inversion-con-republica-dominicana.html</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://listindiario.com/la-republica/gobierno/20251129/china-republica-dominicana-alianza-mueve-comercio-inversion-tecnologia_884203.html</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>https://www.ccrde.org/61-china-ve-enormes-oportunidades-de-comercio-e-inversion-con-republica-dominicana.html</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>https://elnuevodiario.com.do/china-chinos-y-expansion-en-rd-y-ii/</t>
         </is>
@@ -1174,7 +1073,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -1189,7 +1088,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Export-Import Bank of China</t>
+          <t>Export-Import Bank of China (China Eximbank)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1246,25 +1145,20 @@
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>1</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/54799/</t>
+        </is>
+      </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/54799/</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1294,7 +1188,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -1309,7 +1203,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Export-Import Bank of China</t>
+          <t>Export-Import Bank of China (China Eximbank)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Vector</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1361,25 +1260,20 @@
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>1</v>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/54799/</t>
+        </is>
+      </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/54799/</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1409,7 +1303,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -1424,7 +1318,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Export-Import Bank of China</t>
+          <t>Export-Import Bank of China (China Eximbank)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Vector</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1476,25 +1375,20 @@
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BB7" t="n">
         <v>1</v>
       </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/54799/</t>
+        </is>
+      </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/54799/</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1524,7 +1418,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -1539,7 +1433,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Export-Import Bank of China</t>
+          <t>Export-Import Bank of China (China Eximbank)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Vector</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1591,25 +1490,20 @@
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>1</v>
       </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/54799/</t>
+        </is>
+      </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/54799/</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1639,7 +1533,7 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -1654,7 +1548,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Export-Import Bank of China</t>
+          <t>Export-Import Bank of China (China Eximbank)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Vector</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1706,25 +1605,20 @@
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BB9" t="n">
         <v>1</v>
       </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/54799/</t>
+        </is>
+      </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/54799/</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>

--- a/data/sources/countries/dominican_republic.xlsx
+++ b/data/sources/countries/dominican_republic.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE9"/>
+  <dimension ref="A1:BG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -710,6 +719,7 @@
           <t>DOM-0001</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -728,10 +738,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G2" t="n">
+        <v>214</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -782,6 +790,9 @@
       <c r="R2" t="n">
         <v>40</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -797,23 +808,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://presidencia.gob.do/noticias/republica-dominicana-y-la-republica-popular-china-firman-instrumentos-de-cooperacion</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/agencias/2025/09/08/republica-dominicana-y-china-suscriben-un-convenio-de-cooperacion-economica-para-proyectos-de-desarrollo/</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>https://revistamercado.do/money-invest/rd-y-china-acuerdan-cooperacion-por-us40-millones/</t>
         </is>
@@ -825,6 +866,7 @@
           <t>DOM-0002</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -843,10 +885,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G3" t="n">
+        <v>214</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -897,6 +937,9 @@
       <c r="R3" t="n">
         <v>6</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -912,23 +955,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.diariolibre.com/economia/huawei-busca-que-repblica-dominicana-sea-centro-regional-CODL351399</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://hoy.com.do/economia/huawei-dominicana-cierra-2022-con-positivo-balance_941954.html</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://ayuntamientosancristobal.gob.do/el-instituto-dominicano-de-las-telecomunicaciones-indotel-y-huawei-technologies-dominicana-s-r-l-firman-un-acuerdo-para-la-cooperacion-tecnologica/</t>
         </is>
@@ -940,6 +1013,7 @@
           <t>DOM-0003</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>3</v>
       </c>
@@ -958,10 +1032,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G4" t="n">
+        <v>214</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1012,6 +1084,9 @@
       <c r="R4" t="n">
         <v>800</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -1027,23 +1102,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>3</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
         <v>1</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/gobierno/20251129/china-republica-dominicana-alianza-mueve-comercio-inversion-tecnologia_884203.html</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://www.ccrde.org/61-china-ve-enormes-oportunidades-de-comercio-e-inversion-con-republica-dominicana.html</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>https://elnuevodiario.com.do/china-chinos-y-expansion-en-rd-y-ii/</t>
         </is>
@@ -1055,6 +1164,7 @@
           <t>DOM-0004</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>4</v>
       </c>
@@ -1073,10 +1183,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G5" t="n">
+        <v>214</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1127,6 +1235,9 @@
       <c r="R5" t="n">
         <v>600</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1142,23 +1253,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
         <v>1</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/54799/</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1170,6 +1315,7 @@
           <t>DOM-0004</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>4</v>
       </c>
@@ -1188,10 +1334,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G6" t="n">
+        <v>214</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1242,6 +1386,9 @@
       <c r="R6" t="n">
         <v>600</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1257,23 +1404,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
         <v>1</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/54799/</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1285,6 +1466,7 @@
           <t>DOM-0004</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>4</v>
       </c>
@@ -1303,10 +1485,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G7" t="n">
+        <v>214</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1357,6 +1537,9 @@
       <c r="R7" t="n">
         <v>600</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1372,23 +1555,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
         <v>1</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/54799/</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1400,6 +1617,7 @@
           <t>DOM-0004</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>4</v>
       </c>
@@ -1418,10 +1636,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G8" t="n">
+        <v>214</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1472,6 +1688,9 @@
       <c r="R8" t="n">
         <v>600</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1487,23 +1706,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
         <v>1</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/54799/</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
@@ -1515,6 +1768,7 @@
           <t>DOM-0004</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>4</v>
       </c>
@@ -1533,10 +1787,8 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
+      <c r="G9" t="n">
+        <v>214</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1587,6 +1839,9 @@
       <c r="R9" t="n">
         <v>600</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1602,23 +1857,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
         <v>1</v>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/54799/</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>https://www.diariolibre.com/actualidad/republica-dominicana-concierta-prestamo-de-us-600-millones-con-china-para-el-sector-electrico-KJ11188376</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>https://listindiario.com/la-republica/2018/11/06/540652/los-us-600-mm-que-prestara-china-a-rd-para-electricidad-tendran-tasa-entre-el-2-y-3--de-interes.html</t>
         </is>
